--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T15:46:49+00:00</t>
+    <t>2026-03-23T16:01:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1014,7 +1014,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/result_uuid</t>
+    <t>http://openelis-global.org/result_uuid</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -1786,7 +1786,7 @@
     <t>Specimen.identifier.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/sampleItem_uuid</t>
+    <t>http://openelis-global.org/sampleItem_uuid</t>
   </si>
   <si>
     <t>Specimen.identifier:uuid.value</t>
@@ -2476,7 +2476,7 @@
     <t>Organization.identifier:cliaNum.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/org_cliaNum</t>
+    <t>http://openelis-global.org/org_cliaNum</t>
   </si>
   <si>
     <t>Organization.identifier:cliaNum.value</t>
@@ -2509,7 +2509,7 @@
     <t>Organization.identifier:shortName.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/org_shortName</t>
+    <t>http://openelis-global.org/org_shortName</t>
   </si>
   <si>
     <t>Organization.identifier:shortName.value</t>
@@ -2542,7 +2542,7 @@
     <t>Organization.identifier:code.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/org_code</t>
+    <t>http://openelis-global.org/org_code</t>
   </si>
   <si>
     <t>Organization.identifier:code.value</t>
@@ -2572,7 +2572,7 @@
     <t>Organization.identifier:uuid.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/org_uuid</t>
+    <t>http://openelis-global.org/org_uuid</t>
   </si>
   <si>
     <t>Organization.identifier:uuid.value</t>
@@ -3509,7 +3509,7 @@
     <t>DiagnosticReport.identifier.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/analysisResult_uuid</t>
+    <t>http://openelis-global.org/analysisResult_uuid</t>
   </si>
   <si>
     <t>DiagnosticReport.identifier:uuid.value</t>
@@ -3997,7 +3997,7 @@
     <t>Patient.identifier:nationalid.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/pat_nationalId</t>
+    <t>http://openelis-global.org/pat_nationalId</t>
   </si>
   <si>
     <t>Patient.identifier:nationalid.value</t>
@@ -4030,7 +4030,7 @@
     <t>Patient.identifier:subjectnumber.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/pat_subjectNumber</t>
+    <t>http://openelis-global.org/pat_subjectNumber</t>
   </si>
   <si>
     <t>Patient.identifier:subjectnumber.value</t>
@@ -4063,7 +4063,7 @@
     <t>Patient.identifier:stnumber.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/pat_stNumber</t>
+    <t>http://openelis-global.org/pat_stNumber</t>
   </si>
   <si>
     <t>Patient.identifier:stnumber.value</t>
@@ -4096,7 +4096,7 @@
     <t>Patient.identifier:guid.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/pat_guid</t>
+    <t>http://openelis-global.org/pat_guid</t>
   </si>
   <si>
     <t>Patient.identifier:guid.value</t>
@@ -4126,7 +4126,7 @@
     <t>Patient.identifier:uuid.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/pat_uuid</t>
+    <t>http://openelis-global.org/pat_uuid</t>
   </si>
   <si>
     <t>Patient.identifier:uuid.value</t>
@@ -4664,7 +4664,7 @@
     <t>ServiceRequest.identifier.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/analysis_uuid</t>
+    <t>http://openelis-global.org/analysis_uuid</t>
   </si>
   <si>
     <t>ServiceRequest.identifier:uuid.value</t>
@@ -4706,7 +4706,7 @@
     <t>ServiceRequest.identifier:labNo.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/samp_labNo</t>
+    <t>http://openelis-global.org/samp_labNo</t>
   </si>
   <si>
     <t>ServiceRequest.identifier:labNo.value</t>
@@ -7420,7 +7420,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="42.56640625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="36.7890625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="34.26953125" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.13671875" customWidth="true" bestFit="true"/>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T16:01:57+00:00</t>
+    <t>2026-05-11T11:00:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T11:00:24+00:00</t>
+    <t>2026-05-11T11:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
